--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
@@ -593,10 +593,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -605,7 +605,7 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>8.199999999999999</v>
@@ -750,10 +750,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -916,10 +916,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -928,7 +928,7 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>8.199999999999999</v>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
@@ -661,16 +661,19 @@
         <v>30</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>30</v>
       </c>
-      <c r="E2">
-        <v>30</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -684,16 +687,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="H3">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -707,16 +713,19 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -730,16 +739,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>82.34999999999999</v>
+      </c>
+      <c r="H5">
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -753,16 +765,19 @@
         <v>12</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>12</v>
       </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +842,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -853,7 +868,7 @@
         <v>88</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -905,7 +920,7 @@
         <v>82.34999999999999</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
@@ -593,22 +593,22 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>12</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -762,22 +762,22 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>12</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -931,22 +931,22 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>12</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -85,13 +85,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>DANTE GAMALIEL</t>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
   </si>
 </sst>
 </file>
@@ -842,7 +851,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -868,7 +877,7 @@
         <v>88</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -920,7 +929,7 @@
         <v>82.34999999999999</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -937,16 +946,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>92.31</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +965,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -988,24 +997,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920241</v>
+        <v>21330051920334</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920149</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
@@ -920,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>82.34999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1038,7 +1038,7 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
@@ -851,7 +851,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -877,7 +877,7 @@
         <v>88</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -903,7 +903,7 @@
         <v>87.5</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -929,7 +929,7 @@
         <v>88.23999999999999</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -955,7 +955,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20231.xlsx
@@ -851,7 +851,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -877,7 +877,7 @@
         <v>88</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -903,7 +903,7 @@
         <v>87.5</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -929,7 +929,7 @@
         <v>88.23999999999999</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -955,7 +955,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
